--- a/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
+++ b/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$169</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O169"/>
+  <dimension ref="A1:O171"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -592,13 +592,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -662,7 +662,7 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -670,10 +670,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I3" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
@@ -682,41 +680,39 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -739,33 +735,33 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -859,14 +855,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -889,33 +885,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -932,12 +928,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1009,14 +1005,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1039,7 +1035,7 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
@@ -1048,24 +1044,24 @@
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1082,12 +1078,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1159,14 +1155,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1198,11 +1194,11 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1232,12 +1228,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1309,14 +1305,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1348,11 +1344,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1375,19 +1371,19 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1459,14 +1455,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1489,7 +1485,7 @@
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
@@ -1497,10 +1493,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I14" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
@@ -1509,39 +1503,37 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1613,12 +1605,12 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1690,12 +1682,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1767,12 +1759,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1844,12 +1836,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1921,12 +1913,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1998,12 +1990,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2075,12 +2067,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2152,12 +2144,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2229,12 +2221,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2306,12 +2298,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2383,12 +2375,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2460,12 +2452,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2537,12 +2529,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2614,12 +2606,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2691,12 +2683,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2768,12 +2760,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2845,12 +2837,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2922,12 +2914,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2999,12 +2991,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3076,12 +3068,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3153,12 +3145,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3230,12 +3222,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3307,12 +3299,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3384,12 +3376,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3461,12 +3453,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3538,12 +3530,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3615,12 +3607,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3692,12 +3684,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3769,12 +3761,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3846,12 +3838,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3923,12 +3915,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -4000,12 +3992,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4077,12 +4069,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4154,12 +4146,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4231,12 +4223,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4308,12 +4300,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4385,12 +4377,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4462,12 +4454,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4539,12 +4531,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4616,12 +4608,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4693,12 +4685,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4770,12 +4762,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4847,12 +4839,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4924,12 +4916,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -5001,12 +4993,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5078,12 +5070,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5155,12 +5147,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5232,12 +5224,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5309,12 +5301,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5386,12 +5378,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5463,12 +5455,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5540,12 +5532,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5617,12 +5609,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5694,12 +5686,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5771,12 +5763,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5848,12 +5840,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5925,12 +5917,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -6002,12 +5994,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6079,12 +6071,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6156,12 +6148,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6233,12 +6225,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6310,12 +6302,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6387,12 +6379,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6464,12 +6456,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6541,12 +6533,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6618,12 +6610,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6695,12 +6687,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6772,12 +6764,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6849,12 +6841,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6926,12 +6918,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -7003,12 +6995,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7080,12 +7072,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7157,12 +7149,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7234,12 +7226,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7311,12 +7303,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7388,12 +7380,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7465,12 +7457,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7542,12 +7534,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7619,12 +7611,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7696,12 +7688,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7773,12 +7765,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7850,12 +7842,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7927,12 +7919,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -8004,12 +7996,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8081,12 +8073,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8158,12 +8150,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8235,12 +8227,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8312,12 +8304,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8389,12 +8381,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8466,12 +8458,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8543,12 +8535,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8620,12 +8612,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8697,12 +8689,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8774,12 +8766,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8851,12 +8843,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8928,12 +8920,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -9005,12 +8997,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9082,12 +9074,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9159,12 +9151,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9236,12 +9228,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9313,12 +9305,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9390,12 +9382,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9467,12 +9459,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9544,12 +9536,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9621,12 +9613,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9698,12 +9690,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9775,12 +9767,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9852,12 +9844,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9929,12 +9921,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -10006,12 +9998,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10083,12 +10075,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10160,12 +10152,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10237,12 +10229,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10314,12 +10306,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10391,12 +10383,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10468,12 +10460,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10545,12 +10537,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10622,12 +10614,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10699,12 +10691,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10776,12 +10768,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10853,12 +10845,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10930,12 +10922,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -11007,12 +10999,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11084,12 +11076,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11161,12 +11153,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11238,12 +11230,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11315,12 +11307,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11392,12 +11384,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11469,12 +11461,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11546,12 +11538,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11623,12 +11615,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11700,12 +11692,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11777,12 +11769,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11854,12 +11846,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11931,12 +11923,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -12008,12 +12000,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12085,12 +12077,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12162,12 +12154,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12239,12 +12231,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12316,12 +12308,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12393,12 +12385,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12470,12 +12462,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12547,12 +12539,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12624,12 +12616,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12701,12 +12693,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12778,12 +12770,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12855,12 +12847,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12932,12 +12924,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -13009,12 +13001,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13086,12 +13078,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13163,12 +13155,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13240,12 +13232,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13317,12 +13309,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13394,82 +13386,236 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B169" s="2" t="inlineStr">
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E169" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F169" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O169" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>UTD-040</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="inlineStr">
-        <is>
-          <t>Tábua Frios Redonda Giratória</t>
-        </is>
-      </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E170" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F170" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O170" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
         <is>
           <t>4803216111</t>
         </is>
       </c>
-      <c r="F169" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,99</t>
-        </is>
-      </c>
-      <c r="G169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N169" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O169" s="2" t="inlineStr">
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O169"/>
+  <autoFilter ref="A1:O171"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
+++ b/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O171"/>
+  <dimension ref="A1:O173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -600,9 +600,9 @@
       <c r="I2" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -667,20 +667,20 @@
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
@@ -705,14 +705,14 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -738,13 +738,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -808,7 +808,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -816,10 +816,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I5" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
@@ -828,41 +826,39 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -885,33 +881,33 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L6" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -928,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1005,14 +1001,14 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1035,33 +1031,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1078,12 +1074,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1155,14 +1151,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1185,7 +1181,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
@@ -1194,24 +1190,24 @@
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1228,12 +1224,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1305,14 +1301,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1344,11 +1340,11 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1378,12 +1374,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1455,14 +1451,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1494,11 +1490,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1521,19 +1517,19 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1605,14 +1601,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1635,7 +1631,7 @@
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1643,10 +1639,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I16" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
@@ -1655,39 +1649,37 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1759,12 +1751,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1836,12 +1828,12 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1913,12 +1905,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1990,12 +1982,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2067,12 +2059,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2144,12 +2136,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2221,12 +2213,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2298,12 +2290,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2375,12 +2367,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2452,12 +2444,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2529,12 +2521,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2606,12 +2598,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2683,12 +2675,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2760,12 +2752,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2837,12 +2829,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2914,12 +2906,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2991,12 +2983,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3068,12 +3060,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3145,12 +3137,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3222,12 +3214,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3299,12 +3291,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3376,12 +3368,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3453,12 +3445,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3530,12 +3522,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3607,12 +3599,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3684,12 +3676,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3761,12 +3753,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3838,12 +3830,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3915,12 +3907,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3992,12 +3984,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4069,12 +4061,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4146,12 +4138,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4223,12 +4215,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4300,12 +4292,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4377,12 +4369,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4454,12 +4446,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4531,12 +4523,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4608,12 +4600,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4685,12 +4677,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4762,12 +4754,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4839,12 +4831,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4916,12 +4908,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4993,12 +4985,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5070,12 +5062,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5147,12 +5139,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5224,12 +5216,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5301,12 +5293,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5378,12 +5370,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5455,12 +5447,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5532,12 +5524,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5609,12 +5601,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5686,12 +5678,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5763,12 +5755,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5840,12 +5832,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5917,12 +5909,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5994,12 +5986,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6071,12 +6063,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6148,12 +6140,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6225,12 +6217,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6302,12 +6294,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6379,12 +6371,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6456,12 +6448,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6533,12 +6525,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6610,12 +6602,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6687,12 +6679,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6764,12 +6756,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6841,12 +6833,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6918,12 +6910,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6995,12 +6987,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7072,12 +7064,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7149,12 +7141,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7226,12 +7218,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7303,12 +7295,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7380,12 +7372,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7457,12 +7449,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7534,12 +7526,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7611,12 +7603,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7688,12 +7680,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7765,12 +7757,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7842,12 +7834,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7919,12 +7911,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7996,12 +7988,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8073,12 +8065,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8150,12 +8142,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8227,12 +8219,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8304,12 +8296,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8381,12 +8373,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8458,12 +8450,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8535,12 +8527,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8612,12 +8604,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8689,12 +8681,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8766,12 +8758,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8843,12 +8835,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8920,12 +8912,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8997,12 +8989,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9074,12 +9066,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9151,12 +9143,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9228,12 +9220,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9305,12 +9297,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9382,12 +9374,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9459,12 +9451,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9536,12 +9528,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9613,12 +9605,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9690,12 +9682,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9767,12 +9759,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9844,12 +9836,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9921,12 +9913,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9998,12 +9990,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10075,12 +10067,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10152,12 +10144,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10229,12 +10221,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10306,12 +10298,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10383,12 +10375,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10460,12 +10452,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10537,12 +10529,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10614,12 +10606,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10691,12 +10683,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10768,12 +10760,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10845,12 +10837,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10922,12 +10914,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10999,12 +10991,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11076,12 +11068,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11153,12 +11145,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11230,12 +11222,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11307,12 +11299,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11384,12 +11376,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11461,12 +11453,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11538,12 +11530,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11615,12 +11607,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11692,12 +11684,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11769,12 +11761,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11846,12 +11838,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11923,12 +11915,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -12000,12 +11992,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12077,12 +12069,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12154,12 +12146,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12231,12 +12223,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12308,12 +12300,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12385,12 +12377,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12462,12 +12454,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12539,12 +12531,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12616,12 +12608,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12693,12 +12685,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12770,12 +12762,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12847,12 +12839,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12924,12 +12916,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -13001,12 +12993,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13078,12 +13070,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13155,12 +13147,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13232,12 +13224,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13309,12 +13301,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13386,12 +13378,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13463,12 +13455,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13540,82 +13532,236 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B171" s="2" t="inlineStr">
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E171" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F171" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O171" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>UTD-040</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="inlineStr">
-        <is>
-          <t>Tábua Frios Redonda Giratória</t>
-        </is>
-      </c>
-      <c r="E171" s="2" t="inlineStr">
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E172" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F172" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O172" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
         <is>
           <t>4803216111</t>
         </is>
       </c>
-      <c r="F171" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,99</t>
-        </is>
-      </c>
-      <c r="G171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N171" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O171" s="2" t="inlineStr">
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O171"/>
+  <autoFilter ref="A1:O173"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
+++ b/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$173</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O173"/>
+  <dimension ref="A1:O175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,14 +559,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,14 +632,14 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>26/06/2026</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
           <t>25/06/2026</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>24/06/2026</t>
-        </is>
-      </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+          <t>R$ 245,00</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
         <v>2</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>50,0%</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>1</v>
-      </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -746,9 +746,9 @@
       <c r="I4" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,14 +778,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
+          <t>25/06/2026</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
           <t>24/06/2026</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>23/06/2026</t>
-        </is>
-      </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -813,20 +813,20 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>12</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>2</v>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -851,14 +851,14 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -884,13 +884,13 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -924,14 +924,14 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>24/06/2026</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
           <t>23/06/2026</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>22/06/2026</t>
-        </is>
-      </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -962,10 +962,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I7" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -974,41 +972,39 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
-        </is>
-      </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1031,33 +1027,33 @@
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>3</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1074,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
+          <t>23/06/2026</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
           <t>22/06/2026</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1151,14 +1147,14 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
-        </is>
-      </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1181,33 +1177,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>▲ 16,7%</t>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1224,12 +1220,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
+          <t>22/06/2026</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
           <t>21/06/2026</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1301,14 +1297,14 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
-        </is>
-      </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1331,7 +1327,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1340,24 +1336,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>▲ 20,0%</t>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1374,12 +1370,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
+          <t>21/06/2026</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
           <t>20/06/2026</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1451,14 +1447,14 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
-        </is>
-      </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1490,11 +1486,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>▲ 400,0%</t>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1524,12 +1520,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
+          <t>20/06/2026</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
           <t>19/06/2026</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1601,14 +1597,14 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
-        </is>
-      </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1640,11 +1636,11 @@
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>5</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1667,19 +1663,19 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
+          <t>19/06/2026</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
           <t>18/06/2026</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1751,14 +1747,14 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
-        </is>
-      </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
           <t>UTD-040</t>
@@ -1781,7 +1777,7 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1789,10 +1785,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I18" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
@@ -1801,39 +1795,37 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
+          <t>18/06/2026</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
           <t>17/06/2026</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1905,12 +1897,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1982,12 +1974,12 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
+          <t>17/06/2026</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
           <t>16/06/2026</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2059,12 +2051,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2136,12 +2128,12 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
+          <t>16/06/2026</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
           <t>15/06/2026</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2213,12 +2205,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2290,12 +2282,12 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
+          <t>15/06/2026</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>14/06/2026</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2367,12 +2359,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2444,12 +2436,12 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
+          <t>14/06/2026</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
           <t>13/06/2026</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2521,12 +2513,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2598,12 +2590,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
+          <t>13/06/2026</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
           <t>12/06/2026</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2675,12 +2667,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2752,12 +2744,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>12/06/2026</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>11/06/2026</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2829,12 +2821,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2906,12 +2898,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
+          <t>11/06/2026</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
           <t>10/06/2026</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2983,12 +2975,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3060,12 +3052,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
+          <t>10/06/2026</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
           <t>09/06/2026</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3137,12 +3129,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3214,12 +3206,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
+          <t>09/06/2026</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
           <t>08/06/2026</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3291,12 +3283,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3368,12 +3360,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
+          <t>08/06/2026</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
           <t>07/06/2026</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3445,12 +3437,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3522,12 +3514,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
+          <t>07/06/2026</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
           <t>06/06/2026</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3599,12 +3591,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3676,12 +3668,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
+          <t>06/06/2026</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
           <t>05/06/2026</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3753,12 +3745,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3830,12 +3822,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
+          <t>05/06/2026</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
           <t>04/06/2026</t>
-        </is>
-      </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3907,12 +3899,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3984,12 +3976,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
+          <t>04/06/2026</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
           <t>03/06/2026</t>
-        </is>
-      </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4061,12 +4053,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4138,12 +4130,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
+          <t>03/06/2026</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
           <t>02/06/2026</t>
-        </is>
-      </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4215,12 +4207,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4292,12 +4284,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
+          <t>02/06/2026</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
           <t>01/06/2026</t>
-        </is>
-      </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4369,12 +4361,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4446,12 +4438,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
+          <t>01/06/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
           <t>31/05/2026</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4523,12 +4515,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4600,12 +4592,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
+          <t>31/05/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
           <t>30/05/2026</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4677,12 +4669,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4754,12 +4746,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
+          <t>30/05/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
           <t>29/05/2026</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4831,12 +4823,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4908,12 +4900,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
+          <t>29/05/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
           <t>28/05/2026</t>
-        </is>
-      </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4985,12 +4977,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5062,12 +5054,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
+          <t>28/05/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
           <t>27/05/2026</t>
-        </is>
-      </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5139,12 +5131,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5216,12 +5208,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
+          <t>27/05/2026</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
           <t>26/05/2026</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5293,12 +5285,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5370,12 +5362,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
+          <t>26/05/2026</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
           <t>25/05/2026</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5447,12 +5439,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5524,12 +5516,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
+          <t>25/05/2026</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
           <t>24/05/2026</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5601,12 +5593,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5678,12 +5670,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
+          <t>24/05/2026</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
           <t>23/05/2026</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5755,12 +5747,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5832,12 +5824,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
+          <t>23/05/2026</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
           <t>22/05/2026</t>
-        </is>
-      </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5909,12 +5901,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5986,12 +5978,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
+          <t>22/05/2026</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
           <t>21/05/2026</t>
-        </is>
-      </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6063,12 +6055,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6140,12 +6132,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
+          <t>21/05/2026</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
           <t>20/05/2026</t>
-        </is>
-      </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6217,12 +6209,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6294,12 +6286,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
+          <t>20/05/2026</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
           <t>19/05/2026</t>
-        </is>
-      </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6371,12 +6363,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6448,12 +6440,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
+          <t>19/05/2026</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
           <t>18/05/2026</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6525,12 +6517,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6602,12 +6594,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
+          <t>18/05/2026</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
           <t>17/05/2026</t>
-        </is>
-      </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6679,12 +6671,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6756,12 +6748,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
+          <t>17/05/2026</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
           <t>16/05/2026</t>
-        </is>
-      </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6833,12 +6825,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6910,12 +6902,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
+          <t>16/05/2026</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
           <t>15/05/2026</t>
-        </is>
-      </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6987,12 +6979,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7064,12 +7056,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
+          <t>15/05/2026</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
           <t>14/05/2026</t>
-        </is>
-      </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7141,12 +7133,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7218,12 +7210,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
+          <t>14/05/2026</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
           <t>13/05/2026</t>
-        </is>
-      </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7295,12 +7287,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7372,12 +7364,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
+          <t>13/05/2026</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
           <t>12/05/2026</t>
-        </is>
-      </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7449,12 +7441,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7526,12 +7518,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
+          <t>12/05/2026</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
           <t>11/05/2026</t>
-        </is>
-      </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7603,12 +7595,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7680,12 +7672,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
+          <t>11/05/2026</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
           <t>10/05/2026</t>
-        </is>
-      </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7757,12 +7749,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7834,12 +7826,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
+          <t>10/05/2026</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
           <t>09/05/2026</t>
-        </is>
-      </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7911,12 +7903,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7988,12 +7980,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
+          <t>09/05/2026</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
           <t>08/05/2026</t>
-        </is>
-      </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8065,12 +8057,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8142,12 +8134,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
+          <t>08/05/2026</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
           <t>07/05/2026</t>
-        </is>
-      </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8219,12 +8211,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8296,12 +8288,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
+          <t>07/05/2026</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
           <t>06/05/2026</t>
-        </is>
-      </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8373,12 +8365,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8450,12 +8442,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
+          <t>06/05/2026</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
           <t>05/05/2026</t>
-        </is>
-      </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8527,12 +8519,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8604,12 +8596,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
+          <t>05/05/2026</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
           <t>04/05/2026</t>
-        </is>
-      </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8681,12 +8673,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8758,12 +8750,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
+          <t>04/05/2026</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
           <t>03/05/2026</t>
-        </is>
-      </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8835,12 +8827,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8912,12 +8904,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
+          <t>03/05/2026</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
           <t>02/05/2026</t>
-        </is>
-      </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8989,12 +8981,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9066,12 +9058,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
+          <t>02/05/2026</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
           <t>01/05/2026</t>
-        </is>
-      </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9143,12 +9135,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9220,12 +9212,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
+          <t>01/05/2026</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
           <t>30/04/2026</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9297,12 +9289,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9374,12 +9366,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
           <t>29/04/2026</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9451,12 +9443,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9528,12 +9520,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
+          <t>29/04/2026</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
           <t>28/04/2026</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9605,12 +9597,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9682,12 +9674,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
+          <t>28/04/2026</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
           <t>27/04/2026</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9759,12 +9751,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9836,12 +9828,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
+          <t>27/04/2026</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
           <t>26/04/2026</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9913,12 +9905,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9990,12 +9982,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
+          <t>26/04/2026</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
           <t>25/04/2026</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10067,12 +10059,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10144,12 +10136,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
+          <t>25/04/2026</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
           <t>24/04/2026</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10221,12 +10213,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10298,12 +10290,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
+          <t>24/04/2026</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
           <t>23/04/2026</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10375,12 +10367,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10452,12 +10444,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
+          <t>23/04/2026</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
           <t>22/04/2026</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10529,12 +10521,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10606,12 +10598,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
+          <t>22/04/2026</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
           <t>21/04/2026</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10683,12 +10675,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10760,12 +10752,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
+          <t>21/04/2026</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
           <t>20/04/2026</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10837,12 +10829,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10914,12 +10906,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
+          <t>20/04/2026</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
           <t>19/04/2026</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10991,12 +10983,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11068,12 +11060,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
+          <t>19/04/2026</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
           <t>18/04/2026</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11145,12 +11137,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11222,12 +11214,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
+          <t>18/04/2026</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
           <t>17/04/2026</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11299,12 +11291,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11376,12 +11368,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
+          <t>17/04/2026</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
           <t>16/04/2026</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11453,12 +11445,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11530,12 +11522,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
+          <t>16/04/2026</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
           <t>15/04/2026</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11607,12 +11599,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11684,12 +11676,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
+          <t>15/04/2026</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
           <t>14/04/2026</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11761,12 +11753,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11838,12 +11830,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
+          <t>14/04/2026</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
           <t>13/04/2026</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11915,12 +11907,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11992,12 +11984,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
+          <t>13/04/2026</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
           <t>12/04/2026</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12069,12 +12061,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12146,12 +12138,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
+          <t>12/04/2026</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
           <t>11/04/2026</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12223,12 +12215,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12300,12 +12292,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
+          <t>11/04/2026</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
           <t>10/04/2026</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12377,12 +12369,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12454,12 +12446,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
+          <t>10/04/2026</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
           <t>09/04/2026</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12531,12 +12523,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12608,12 +12600,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
+          <t>09/04/2026</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
           <t>08/04/2026</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12685,12 +12677,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12762,12 +12754,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
+          <t>08/04/2026</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
           <t>07/04/2026</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12839,12 +12831,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12916,12 +12908,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
+          <t>07/04/2026</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
           <t>06/04/2026</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12993,12 +12985,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13070,12 +13062,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
+          <t>06/04/2026</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
           <t>05/04/2026</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13147,12 +13139,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13224,12 +13216,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
           <t>04/04/2026</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>03/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13301,12 +13293,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13378,12 +13370,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
           <t>03/04/2026</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>02/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13455,12 +13447,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13532,12 +13524,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
           <t>02/04/2026</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>01/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13609,12 +13601,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>31/03/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13686,82 +13678,236 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B173" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B173" s="2" t="inlineStr">
+      <c r="C173" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D173" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E173" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F173" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O173" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B174" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C173" s="2" t="inlineStr">
-        <is>
-          <t>UTD-040</t>
-        </is>
-      </c>
-      <c r="D173" s="2" t="inlineStr">
-        <is>
-          <t>Tábua Frios Redonda Giratória</t>
-        </is>
-      </c>
-      <c r="E173" s="2" t="inlineStr">
+      <c r="C174" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D174" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E174" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F174" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O174" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
         <is>
           <t>4803216111</t>
         </is>
       </c>
-      <c r="F173" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,99</t>
-        </is>
-      </c>
-      <c r="G173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N173" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O173" s="2" t="inlineStr">
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O173"/>
+  <autoFilter ref="A1:O175"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
+++ b/saida_skus/SKU_UTD-040-TABUA-FRIOS-REDONDA-GIRATORIA.xlsx
@@ -10,7 +10,7 @@
     <sheet name="Analise" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$175</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Analise'!$A$1:$O$183</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O175"/>
+  <dimension ref="A1:O183"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -559,12 +559,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -598,11 +598,11 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+        <v>2</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -632,12 +632,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26/06/2026</t>
+          <t>30/06/2026</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -662,33 +662,33 @@
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>R$ 245,00</t>
-        </is>
-      </c>
-      <c r="H3" s="4" t="inlineStr">
-        <is>
-          <t>▲ 600,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H3" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>▼ 50,0%</t>
+        <v>8</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>▲ 700,0%</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>200,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L3" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N3" s="2" t="inlineStr">
@@ -705,12 +705,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -744,11 +744,11 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
+        <v>0</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -778,12 +778,12 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>25/06/2026</t>
+          <t>29/06/2026</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -808,25 +808,25 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 70,00</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>-</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>▼ 83,3%</t>
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="L5" s="2" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -851,12 +851,12 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -890,11 +890,11 @@
         </is>
       </c>
       <c r="I6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>3</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -924,12 +924,12 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>24/06/2026</t>
+          <t>28/06/2026</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -963,7 +963,7 @@
         </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
@@ -972,15 +972,15 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1030,17 +1030,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 100,0%</t>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>▼ 66,7%</t>
+        <v>0</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1070,12 +1070,12 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>23/06/2026</t>
+          <t>27/06/2026</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1100,59 +1100,55 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1177,33 +1173,33 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>R$ 140,00</t>
-        </is>
-      </c>
-      <c r="H10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 300,0%</t>
+          <t>R$ 0,00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="I10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>▲ 28,6%</t>
+        <v>0</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1220,12 +1216,12 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>22/06/2026</t>
+          <t>26/06/2026</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1250,59 +1246,55 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 245,00</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>▲ 600,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>▼ 50,0%</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>200,0%</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1327,7 +1319,7 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>R$ 35,00</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1336,24 +1328,24 @@
         </is>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>▲ 16,7%</t>
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="L12" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1370,12 +1362,12 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>21/06/2026</t>
+          <t>25/06/2026</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1400,59 +1392,55 @@
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>▼ 83,3%</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>50,0%</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -1486,11 +1474,11 @@
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>▲ 20,0%</t>
+        <v>1</v>
+      </c>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1520,12 +1508,12 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>20/06/2026</t>
+          <t>24/06/2026</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -1550,7 +1538,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -1558,10 +1546,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I15" s="2" t="n">
+        <v>12</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
@@ -1570,39 +1556,37 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>8,3%</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -1630,17 +1614,17 @@
           <t>R$ 0,00</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="H16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 100,0%</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>▲ 400,0%</t>
+        <v>3</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>▼ 66,7%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1670,12 +1654,12 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>19/06/2026</t>
+          <t>23/06/2026</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -1747,12 +1731,12 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
@@ -1777,33 +1761,33 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>R$ 0,00</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>R$ 140,00</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 300,0%</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+        <v>9</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>▲ 28,6%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>44,4%</t>
         </is>
       </c>
       <c r="L18" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -1813,19 +1797,19 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>Sem calcular</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>18/06/2026</t>
+          <t>22/06/2026</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
@@ -1897,12 +1881,12 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -1927,7 +1911,7 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 35,00</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
@@ -1935,51 +1919,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>▲ 16,7%</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>14,3%</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>17/06/2026</t>
+          <t>21/06/2026</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2051,12 +2031,12 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
@@ -2081,7 +2061,7 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2089,51 +2069,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I22" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>▲ 20,0%</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>16/06/2026</t>
+          <t>20/06/2026</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
@@ -2205,12 +2181,12 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
@@ -2235,7 +2211,7 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2243,51 +2219,47 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
+      <c r="I24" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>▲ 400,0%</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Ruim</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>15/06/2026</t>
+          <t>19/06/2026</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="C25" s="2" t="inlineStr">
@@ -2359,12 +2331,12 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2389,7 +2361,7 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>R$ 0,00</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
@@ -2397,10 +2369,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="I26" s="2" t="n">
+        <v>1</v>
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
@@ -2409,39 +2379,37 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>0</v>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Básica</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Sem calcular</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>14/06/2026</t>
+          <t>18/06/2026</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
@@ -2513,12 +2481,12 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
@@ -2590,12 +2558,12 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>13/06/2026</t>
+          <t>17/06/2026</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="C29" s="2" t="inlineStr">
@@ -2667,12 +2635,12 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C30" s="2" t="inlineStr">
@@ -2744,12 +2712,12 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>12/06/2026</t>
+          <t>16/06/2026</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -2821,12 +2789,12 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -2898,12 +2866,12 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>11/06/2026</t>
+          <t>15/06/2026</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -2975,12 +2943,12 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3052,12 +3020,12 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>10/06/2026</t>
+          <t>14/06/2026</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3129,12 +3097,12 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3206,12 +3174,12 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>09/06/2026</t>
+          <t>13/06/2026</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3283,12 +3251,12 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
@@ -3360,12 +3328,12 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08/06/2026</t>
+          <t>12/06/2026</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
@@ -3437,12 +3405,12 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3514,12 +3482,12 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07/06/2026</t>
+          <t>11/06/2026</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3591,12 +3559,12 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
@@ -3668,12 +3636,12 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06/06/2026</t>
+          <t>10/06/2026</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="C43" s="2" t="inlineStr">
@@ -3745,12 +3713,12 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3822,12 +3790,12 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>05/06/2026</t>
+          <t>09/06/2026</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3899,12 +3867,12 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3976,12 +3944,12 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>04/06/2026</t>
+          <t>08/06/2026</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -4053,12 +4021,12 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4130,12 +4098,12 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>03/06/2026</t>
+          <t>07/06/2026</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4207,12 +4175,12 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4284,12 +4252,12 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>02/06/2026</t>
+          <t>06/06/2026</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4361,12 +4329,12 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4438,12 +4406,12 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>01/06/2026</t>
+          <t>05/06/2026</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4515,12 +4483,12 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4592,12 +4560,12 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>31/05/2026</t>
+          <t>04/06/2026</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4669,12 +4637,12 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
@@ -4746,12 +4714,12 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>30/05/2026</t>
+          <t>03/06/2026</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
@@ -4823,12 +4791,12 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -4900,12 +4868,12 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>29/05/2026</t>
+          <t>02/06/2026</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="C59" s="2" t="inlineStr">
@@ -4977,12 +4945,12 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C60" s="2" t="inlineStr">
@@ -5054,12 +5022,12 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>28/05/2026</t>
+          <t>01/06/2026</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
@@ -5131,12 +5099,12 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
@@ -5208,12 +5176,12 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>27/05/2026</t>
+          <t>31/05/2026</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
@@ -5285,12 +5253,12 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
@@ -5362,12 +5330,12 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>26/05/2026</t>
+          <t>30/05/2026</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
@@ -5439,12 +5407,12 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
@@ -5516,12 +5484,12 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>25/05/2026</t>
+          <t>29/05/2026</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
@@ -5593,12 +5561,12 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C68" s="2" t="inlineStr">
@@ -5670,12 +5638,12 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24/05/2026</t>
+          <t>28/05/2026</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="C69" s="2" t="inlineStr">
@@ -5747,12 +5715,12 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C70" s="2" t="inlineStr">
@@ -5824,12 +5792,12 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23/05/2026</t>
+          <t>27/05/2026</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="C71" s="2" t="inlineStr">
@@ -5901,12 +5869,12 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C72" s="2" t="inlineStr">
@@ -5978,12 +5946,12 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>22/05/2026</t>
+          <t>26/05/2026</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
@@ -6055,12 +6023,12 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C74" s="2" t="inlineStr">
@@ -6132,12 +6100,12 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>21/05/2026</t>
+          <t>25/05/2026</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="C75" s="2" t="inlineStr">
@@ -6209,12 +6177,12 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C76" s="2" t="inlineStr">
@@ -6286,12 +6254,12 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>20/05/2026</t>
+          <t>24/05/2026</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="C77" s="2" t="inlineStr">
@@ -6363,12 +6331,12 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C78" s="2" t="inlineStr">
@@ -6440,12 +6408,12 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>19/05/2026</t>
+          <t>23/05/2026</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="C79" s="2" t="inlineStr">
@@ -6517,12 +6485,12 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C80" s="2" t="inlineStr">
@@ -6594,12 +6562,12 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>18/05/2026</t>
+          <t>22/05/2026</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="C81" s="2" t="inlineStr">
@@ -6671,12 +6639,12 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C82" s="2" t="inlineStr">
@@ -6748,12 +6716,12 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>17/05/2026</t>
+          <t>21/05/2026</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="C83" s="2" t="inlineStr">
@@ -6825,12 +6793,12 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C84" s="2" t="inlineStr">
@@ -6902,12 +6870,12 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>16/05/2026</t>
+          <t>20/05/2026</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="C85" s="2" t="inlineStr">
@@ -6979,12 +6947,12 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C86" s="2" t="inlineStr">
@@ -7056,12 +7024,12 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15/05/2026</t>
+          <t>19/05/2026</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="C87" s="2" t="inlineStr">
@@ -7133,12 +7101,12 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C88" s="2" t="inlineStr">
@@ -7210,12 +7178,12 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14/05/2026</t>
+          <t>18/05/2026</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="C89" s="2" t="inlineStr">
@@ -7287,12 +7255,12 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C90" s="2" t="inlineStr">
@@ -7364,12 +7332,12 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>13/05/2026</t>
+          <t>17/05/2026</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="C91" s="2" t="inlineStr">
@@ -7441,12 +7409,12 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C92" s="2" t="inlineStr">
@@ -7518,12 +7486,12 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>12/05/2026</t>
+          <t>16/05/2026</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="C93" s="2" t="inlineStr">
@@ -7595,12 +7563,12 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C94" s="2" t="inlineStr">
@@ -7672,12 +7640,12 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>11/05/2026</t>
+          <t>15/05/2026</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="C95" s="2" t="inlineStr">
@@ -7749,12 +7717,12 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C96" s="2" t="inlineStr">
@@ -7826,12 +7794,12 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>10/05/2026</t>
+          <t>14/05/2026</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="C97" s="2" t="inlineStr">
@@ -7903,12 +7871,12 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C98" s="2" t="inlineStr">
@@ -7980,12 +7948,12 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>09/05/2026</t>
+          <t>13/05/2026</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="C99" s="2" t="inlineStr">
@@ -8057,12 +8025,12 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C100" s="2" t="inlineStr">
@@ -8134,12 +8102,12 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>08/05/2026</t>
+          <t>12/05/2026</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="C101" s="2" t="inlineStr">
@@ -8211,12 +8179,12 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C102" s="2" t="inlineStr">
@@ -8288,12 +8256,12 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>07/05/2026</t>
+          <t>11/05/2026</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="C103" s="2" t="inlineStr">
@@ -8365,12 +8333,12 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C104" s="2" t="inlineStr">
@@ -8442,12 +8410,12 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>06/05/2026</t>
+          <t>10/05/2026</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="C105" s="2" t="inlineStr">
@@ -8519,12 +8487,12 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C106" s="2" t="inlineStr">
@@ -8596,12 +8564,12 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>05/05/2026</t>
+          <t>09/05/2026</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="C107" s="2" t="inlineStr">
@@ -8673,12 +8641,12 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C108" s="2" t="inlineStr">
@@ -8750,12 +8718,12 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>04/05/2026</t>
+          <t>08/05/2026</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="C109" s="2" t="inlineStr">
@@ -8827,12 +8795,12 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C110" s="2" t="inlineStr">
@@ -8904,12 +8872,12 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>03/05/2026</t>
+          <t>07/05/2026</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="C111" s="2" t="inlineStr">
@@ -8981,12 +8949,12 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C112" s="2" t="inlineStr">
@@ -9058,12 +9026,12 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02/05/2026</t>
+          <t>06/05/2026</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="C113" s="2" t="inlineStr">
@@ -9135,12 +9103,12 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C114" s="2" t="inlineStr">
@@ -9212,12 +9180,12 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>01/05/2026</t>
+          <t>05/05/2026</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="C115" s="2" t="inlineStr">
@@ -9289,12 +9257,12 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C116" s="2" t="inlineStr">
@@ -9366,12 +9334,12 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>30/04/2026</t>
+          <t>04/05/2026</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="C117" s="2" t="inlineStr">
@@ -9443,12 +9411,12 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C118" s="2" t="inlineStr">
@@ -9520,12 +9488,12 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>29/04/2026</t>
+          <t>03/05/2026</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="C119" s="2" t="inlineStr">
@@ -9597,12 +9565,12 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C120" s="2" t="inlineStr">
@@ -9674,12 +9642,12 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28/04/2026</t>
+          <t>02/05/2026</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="C121" s="2" t="inlineStr">
@@ -9751,12 +9719,12 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C122" s="2" t="inlineStr">
@@ -9828,12 +9796,12 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>01/05/2026</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="C123" s="2" t="inlineStr">
@@ -9905,12 +9873,12 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C124" s="2" t="inlineStr">
@@ -9982,12 +9950,12 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>26/04/2026</t>
+          <t>30/04/2026</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="C125" s="2" t="inlineStr">
@@ -10059,12 +10027,12 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C126" s="2" t="inlineStr">
@@ -10136,12 +10104,12 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>25/04/2026</t>
+          <t>29/04/2026</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="C127" s="2" t="inlineStr">
@@ -10213,12 +10181,12 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C128" s="2" t="inlineStr">
@@ -10290,12 +10258,12 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>24/04/2026</t>
+          <t>28/04/2026</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="C129" s="2" t="inlineStr">
@@ -10367,12 +10335,12 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C130" s="2" t="inlineStr">
@@ -10444,12 +10412,12 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="C131" s="2" t="inlineStr">
@@ -10521,12 +10489,12 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C132" s="2" t="inlineStr">
@@ -10598,12 +10566,12 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>22/04/2026</t>
+          <t>26/04/2026</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="C133" s="2" t="inlineStr">
@@ -10675,12 +10643,12 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C134" s="2" t="inlineStr">
@@ -10752,12 +10720,12 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>21/04/2026</t>
+          <t>25/04/2026</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="C135" s="2" t="inlineStr">
@@ -10829,12 +10797,12 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C136" s="2" t="inlineStr">
@@ -10906,12 +10874,12 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>20/04/2026</t>
+          <t>24/04/2026</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="C137" s="2" t="inlineStr">
@@ -10983,12 +10951,12 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C138" s="2" t="inlineStr">
@@ -11060,12 +11028,12 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>19/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="C139" s="2" t="inlineStr">
@@ -11137,12 +11105,12 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C140" s="2" t="inlineStr">
@@ -11214,12 +11182,12 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>18/04/2026</t>
+          <t>22/04/2026</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="C141" s="2" t="inlineStr">
@@ -11291,12 +11259,12 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C142" s="2" t="inlineStr">
@@ -11368,12 +11336,12 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>17/04/2026</t>
+          <t>21/04/2026</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="C143" s="2" t="inlineStr">
@@ -11445,12 +11413,12 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C144" s="2" t="inlineStr">
@@ -11522,12 +11490,12 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>16/04/2026</t>
+          <t>20/04/2026</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="C145" s="2" t="inlineStr">
@@ -11599,12 +11567,12 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C146" s="2" t="inlineStr">
@@ -11676,12 +11644,12 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>15/04/2026</t>
+          <t>19/04/2026</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="C147" s="2" t="inlineStr">
@@ -11753,12 +11721,12 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C148" s="2" t="inlineStr">
@@ -11830,12 +11798,12 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>18/04/2026</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="C149" s="2" t="inlineStr">
@@ -11907,12 +11875,12 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C150" s="2" t="inlineStr">
@@ -11984,12 +11952,12 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13/04/2026</t>
+          <t>17/04/2026</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="C151" s="2" t="inlineStr">
@@ -12061,12 +12029,12 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C152" s="2" t="inlineStr">
@@ -12138,12 +12106,12 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>12/04/2026</t>
+          <t>16/04/2026</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="C153" s="2" t="inlineStr">
@@ -12215,12 +12183,12 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C154" s="2" t="inlineStr">
@@ -12292,12 +12260,12 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>11/04/2026</t>
+          <t>15/04/2026</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="C155" s="2" t="inlineStr">
@@ -12369,12 +12337,12 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C156" s="2" t="inlineStr">
@@ -12446,12 +12414,12 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>10/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="C157" s="2" t="inlineStr">
@@ -12523,12 +12491,12 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C158" s="2" t="inlineStr">
@@ -12600,12 +12568,12 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>09/04/2026</t>
+          <t>13/04/2026</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="C159" s="2" t="inlineStr">
@@ -12677,12 +12645,12 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C160" s="2" t="inlineStr">
@@ -12754,12 +12722,12 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>08/04/2026</t>
+          <t>12/04/2026</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="C161" s="2" t="inlineStr">
@@ -12831,12 +12799,12 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C162" s="2" t="inlineStr">
@@ -12908,12 +12876,12 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>07/04/2026</t>
+          <t>11/04/2026</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="C163" s="2" t="inlineStr">
@@ -12985,12 +12953,12 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C164" s="2" t="inlineStr">
@@ -13062,12 +13030,12 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>06/04/2026</t>
+          <t>10/04/2026</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="C165" s="2" t="inlineStr">
@@ -13139,12 +13107,12 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C166" s="2" t="inlineStr">
@@ -13216,12 +13184,12 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>05/04/2026</t>
+          <t>09/04/2026</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="C167" s="2" t="inlineStr">
@@ -13293,12 +13261,12 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C168" s="2" t="inlineStr">
@@ -13370,12 +13338,12 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>04/04/2026</t>
+          <t>08/04/2026</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="C169" s="2" t="inlineStr">
@@ -13447,12 +13415,12 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C170" s="2" t="inlineStr">
@@ -13524,12 +13492,12 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>03/04/2026</t>
+          <t>07/04/2026</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="C171" s="2" t="inlineStr">
@@ -13601,12 +13569,12 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C172" s="2" t="inlineStr">
@@ -13678,12 +13646,12 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>02/04/2026</t>
+          <t>06/04/2026</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="C173" s="2" t="inlineStr">
@@ -13755,12 +13723,12 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>01/04/2026</t>
+          <t>05/04/2026</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>31/03/2026</t>
+          <t>04/04/2026</t>
         </is>
       </c>
       <c r="C174" s="2" t="inlineStr">
@@ -13832,82 +13800,698 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
+          <t>05/04/2026</t>
+        </is>
+      </c>
+      <c r="B175" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="C175" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D175" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E175" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F175" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O175" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B176" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C176" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D176" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E176" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F176" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O176" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="2" t="inlineStr">
+        <is>
+          <t>04/04/2026</t>
+        </is>
+      </c>
+      <c r="B177" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="C177" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D177" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E177" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F177" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O177" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B178" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C178" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D178" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E178" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F178" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O178" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="inlineStr">
+        <is>
+          <t>03/04/2026</t>
+        </is>
+      </c>
+      <c r="B179" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="C179" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D179" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E179" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F179" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O179" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B180" s="2" t="inlineStr">
+        <is>
           <t>01/04/2026</t>
         </is>
       </c>
-      <c r="B175" s="2" t="inlineStr">
+      <c r="C180" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D180" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E180" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F180" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O180" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="inlineStr">
+        <is>
+          <t>02/04/2026</t>
+        </is>
+      </c>
+      <c r="B181" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="C181" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D181" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E181" s="2" t="inlineStr">
+        <is>
+          <t>4803216111</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O181" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B182" s="2" t="inlineStr">
         <is>
           <t>31/03/2026</t>
         </is>
       </c>
-      <c r="C175" s="2" t="inlineStr">
-        <is>
-          <t>UTD-040</t>
-        </is>
-      </c>
-      <c r="D175" s="2" t="inlineStr">
-        <is>
-          <t>Tábua Frios Redonda Giratória</t>
-        </is>
-      </c>
-      <c r="E175" s="2" t="inlineStr">
+      <c r="C182" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D182" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E182" s="2" t="inlineStr">
+        <is>
+          <t>4786400917</t>
+        </is>
+      </c>
+      <c r="F182" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O182" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="inlineStr">
+        <is>
+          <t>01/04/2026</t>
+        </is>
+      </c>
+      <c r="B183" s="2" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C183" s="2" t="inlineStr">
+        <is>
+          <t>UTD-040</t>
+        </is>
+      </c>
+      <c r="D183" s="2" t="inlineStr">
+        <is>
+          <t>Tábua Frios Redonda Giratória</t>
+        </is>
+      </c>
+      <c r="E183" s="2" t="inlineStr">
         <is>
           <t>4803216111</t>
         </is>
       </c>
-      <c r="F175" s="2" t="inlineStr">
-        <is>
-          <t>R$ 69,99</t>
-        </is>
-      </c>
-      <c r="G175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N175" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="O175" s="2" t="inlineStr">
+      <c r="F183" s="2" t="inlineStr">
+        <is>
+          <t>R$ 69,99</t>
+        </is>
+      </c>
+      <c r="G183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N183" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O183" s="2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O175"/>
+  <autoFilter ref="A1:O183"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>